--- a/downloads/planes_inversion.xlsx
+++ b/downloads/planes_inversion.xlsx
@@ -412,7 +412,7 @@
         <v>37</v>
       </c>
       <c r="F2">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -441,7 +441,7 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -470,7 +470,7 @@
         <v>527</v>
       </c>
       <c r="F4">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -499,7 +499,7 @@
         <v>527</v>
       </c>
       <c r="F5">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -528,7 +528,7 @@
         <v>527</v>
       </c>
       <c r="F6">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -551,13 +551,13 @@
         </is>
       </c>
       <c r="D7">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="F7">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -583,10 +583,10 @@
         <v>14</v>
       </c>
       <c r="E8">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="F8">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>595</v>
+        <v>612</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         <v>252</v>
       </c>
       <c r="F10">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>92</v>
       </c>
       <c r="F11">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -699,10 +699,10 @@
         <v>419</v>
       </c>
       <c r="E12">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="F12">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -728,10 +728,10 @@
         <v>948</v>
       </c>
       <c r="E13">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="F13">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -757,10 +757,10 @@
         <v>105</v>
       </c>
       <c r="E14">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="F14">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -783,13 +783,13 @@
         </is>
       </c>
       <c r="D15">
-        <v>1565</v>
+        <v>1574</v>
       </c>
       <c r="E15">
-        <v>1793</v>
+        <v>1802</v>
       </c>
       <c r="F15">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -815,10 +815,10 @@
         <v>228</v>
       </c>
       <c r="E16">
-        <v>1793</v>
+        <v>1802</v>
       </c>
       <c r="F16">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>82</v>
       </c>
       <c r="F17">
-        <v>3691</v>
+        <v>3701</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>162</v>
       </c>
       <c r="F18">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>74</v>
       </c>
       <c r="F19">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>2579</v>
       </c>
       <c r="F20">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>2579</v>
       </c>
       <c r="F21">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>2579</v>
       </c>
       <c r="F22">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1015,13 +1015,13 @@
         </is>
       </c>
       <c r="D23">
-        <v>2277</v>
+        <v>2348</v>
       </c>
       <c r="E23">
-        <v>2653</v>
+        <v>2724</v>
       </c>
       <c r="F23">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
         <v>376</v>
       </c>
       <c r="E24">
-        <v>2653</v>
+        <v>2724</v>
       </c>
       <c r="F24">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>130</v>
       </c>
       <c r="F25">
-        <v>5598</v>
+        <v>5669</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>36</v>
       </c>
       <c r="F26">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>64</v>
       </c>
       <c r="F27">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>3875</v>
       </c>
       <c r="F28">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1195,7 +1195,7 @@
         <v>3875</v>
       </c>
       <c r="F29">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1224,7 +1224,7 @@
         <v>3875</v>
       </c>
       <c r="F30">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1247,13 +1247,13 @@
         </is>
       </c>
       <c r="D31">
-        <v>959</v>
+        <v>1090</v>
       </c>
       <c r="E31">
-        <v>1501</v>
+        <v>1632</v>
       </c>
       <c r="F31">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1279,10 +1279,10 @@
         <v>542</v>
       </c>
       <c r="E32">
-        <v>1501</v>
+        <v>1632</v>
       </c>
       <c r="F32">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1311,7 +1311,7 @@
         <v>66</v>
       </c>
       <c r="F33">
-        <v>5542</v>
+        <v>5673</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1340,7 +1340,7 @@
         <v>0</v>
       </c>
       <c r="F34">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>24</v>
       </c>
       <c r="F35">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>4128</v>
       </c>
       <c r="F36">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>4128</v>
       </c>
       <c r="F37">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1456,7 +1456,7 @@
         <v>4128</v>
       </c>
       <c r="F38">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1479,13 +1479,13 @@
         </is>
       </c>
       <c r="D39">
-        <v>680</v>
+        <v>818</v>
       </c>
       <c r="E39">
-        <v>1171</v>
+        <v>1309</v>
       </c>
       <c r="F39">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
         <v>491</v>
       </c>
       <c r="E40">
-        <v>1171</v>
+        <v>1309</v>
       </c>
       <c r="F40">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1543,7 +1543,7 @@
         <v>8</v>
       </c>
       <c r="F41">
-        <v>5331</v>
+        <v>5469</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>

--- a/downloads/planes_inversion.xlsx
+++ b/downloads/planes_inversion.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G265"/>
+  <dimension ref="A1:G269"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -876,7 +876,7 @@
         <v>162</v>
       </c>
       <c r="F18">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>74</v>
       </c>
       <c r="F19">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -934,7 +934,7 @@
         <v>2579</v>
       </c>
       <c r="F20">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -963,7 +963,7 @@
         <v>2579</v>
       </c>
       <c r="F21">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>2579</v>
       </c>
       <c r="F22">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1011,17 +1011,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Fertilizantes</t>
         </is>
       </c>
       <c r="D23">
-        <v>2348</v>
+        <v>527</v>
       </c>
       <c r="E23">
-        <v>2724</v>
+        <v>3251</v>
       </c>
       <c r="F23">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1040,17 +1040,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D24">
-        <v>376</v>
+        <v>2348</v>
       </c>
       <c r="E24">
-        <v>2724</v>
+        <v>3251</v>
       </c>
       <c r="F24">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1064,22 +1064,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D25">
-        <v>130</v>
+        <v>376</v>
       </c>
       <c r="E25">
-        <v>130</v>
+        <v>3251</v>
       </c>
       <c r="F25">
-        <v>5669</v>
+        <v>6196</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1089,26 +1089,26 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D26">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="E26">
-        <v>36</v>
+        <v>130</v>
       </c>
       <c r="F26">
-        <v>5673</v>
+        <v>6196</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1122,22 +1122,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D27">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="E27">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="F27">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1151,22 +1151,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D28">
-        <v>2362</v>
+        <v>64</v>
       </c>
       <c r="E28">
-        <v>3875</v>
+        <v>64</v>
       </c>
       <c r="F28">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1185,17 +1185,17 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D29">
-        <v>1141</v>
+        <v>2362</v>
       </c>
       <c r="E29">
         <v>3875</v>
       </c>
       <c r="F29">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1214,17 +1214,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D30">
-        <v>372</v>
+        <v>1141</v>
       </c>
       <c r="E30">
         <v>3875</v>
       </c>
       <c r="F30">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1238,22 +1238,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D31">
-        <v>1090</v>
+        <v>372</v>
       </c>
       <c r="E31">
-        <v>1632</v>
+        <v>3875</v>
       </c>
       <c r="F31">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1272,17 +1272,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Fertilizantes</t>
         </is>
       </c>
       <c r="D32">
-        <v>542</v>
+        <v>578</v>
       </c>
       <c r="E32">
-        <v>1632</v>
+        <v>2210</v>
       </c>
       <c r="F32">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1296,22 +1296,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D33">
-        <v>66</v>
+        <v>1090</v>
       </c>
       <c r="E33">
-        <v>66</v>
+        <v>2210</v>
       </c>
       <c r="F33">
-        <v>5673</v>
+        <v>6251</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1321,26 +1321,26 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>542</v>
       </c>
       <c r="E34">
-        <v>0</v>
+        <v>2210</v>
       </c>
       <c r="F34">
-        <v>5469</v>
+        <v>6251</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1350,26 +1350,26 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D35">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="E35">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="F35">
-        <v>5469</v>
+        <v>6251</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1383,22 +1383,22 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D36">
-        <v>2999</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>4128</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <v>5469</v>
+        <v>6644</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1412,22 +1412,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D37">
-        <v>749</v>
+        <v>24</v>
       </c>
       <c r="E37">
-        <v>4128</v>
+        <v>24</v>
       </c>
       <c r="F37">
-        <v>5469</v>
+        <v>6644</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1446,17 +1446,17 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D38">
-        <v>380</v>
+        <v>2999</v>
       </c>
       <c r="E38">
         <v>4128</v>
       </c>
       <c r="F38">
-        <v>5469</v>
+        <v>6644</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1470,22 +1470,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D39">
-        <v>818</v>
+        <v>749</v>
       </c>
       <c r="E39">
-        <v>1309</v>
+        <v>4128</v>
       </c>
       <c r="F39">
-        <v>5469</v>
+        <v>6644</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1499,22 +1499,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D40">
-        <v>491</v>
+        <v>380</v>
       </c>
       <c r="E40">
-        <v>1309</v>
+        <v>4128</v>
       </c>
       <c r="F40">
-        <v>5469</v>
+        <v>6644</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1528,22 +1528,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Fertilizantes</t>
         </is>
       </c>
       <c r="D41">
-        <v>8</v>
+        <v>1175</v>
       </c>
       <c r="E41">
-        <v>8</v>
+        <v>2484</v>
       </c>
       <c r="F41">
-        <v>5469</v>
+        <v>6644</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1553,26 +1553,26 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D42">
-        <v>0</v>
+        <v>818</v>
       </c>
       <c r="E42">
-        <v>0</v>
+        <v>2484</v>
       </c>
       <c r="F42">
-        <v>4252</v>
+        <v>6644</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1582,26 +1582,26 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D43">
-        <v>21</v>
+        <v>491</v>
       </c>
       <c r="E43">
-        <v>21</v>
+        <v>2484</v>
       </c>
       <c r="F43">
-        <v>4252</v>
+        <v>6644</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1611,26 +1611,26 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>2029</v>
+        <v>2028</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D44">
-        <v>2843</v>
+        <v>8</v>
       </c>
       <c r="E44">
-        <v>3278</v>
+        <v>8</v>
       </c>
       <c r="F44">
-        <v>4252</v>
+        <v>6644</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1644,22 +1644,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D45">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>3278</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <v>4252</v>
+        <v>4665</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1673,22 +1673,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D46">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="E46">
-        <v>3278</v>
+        <v>21</v>
       </c>
       <c r="F46">
-        <v>4252</v>
+        <v>4665</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1702,22 +1702,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D47">
-        <v>685</v>
+        <v>2843</v>
       </c>
       <c r="E47">
-        <v>953</v>
+        <v>3278</v>
       </c>
       <c r="F47">
-        <v>4252</v>
+        <v>4665</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1731,22 +1731,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D48">
-        <v>268</v>
+        <v>229</v>
       </c>
       <c r="E48">
-        <v>953</v>
+        <v>3278</v>
       </c>
       <c r="F48">
-        <v>4252</v>
+        <v>4665</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1760,22 +1760,22 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>206</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>3278</v>
       </c>
       <c r="F49">
-        <v>4252</v>
+        <v>4665</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -1785,26 +1785,26 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Fertilizantes</t>
         </is>
       </c>
       <c r="D50">
-        <v>0</v>
+        <v>413</v>
       </c>
       <c r="E50">
-        <v>0</v>
+        <v>1366</v>
       </c>
       <c r="F50">
-        <v>3485</v>
+        <v>4665</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1814,26 +1814,26 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D51">
-        <v>2</v>
+        <v>685</v>
       </c>
       <c r="E51">
-        <v>2</v>
+        <v>1366</v>
       </c>
       <c r="F51">
-        <v>3485</v>
+        <v>4665</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -1843,26 +1843,26 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D52">
-        <v>2223</v>
+        <v>268</v>
       </c>
       <c r="E52">
-        <v>2450</v>
+        <v>1366</v>
       </c>
       <c r="F52">
-        <v>3485</v>
+        <v>4665</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -1872,26 +1872,26 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D53">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>2450</v>
+        <v>0</v>
       </c>
       <c r="F53">
-        <v>3485</v>
+        <v>4665</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -1905,19 +1905,19 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D54">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>2450</v>
+        <v>0</v>
       </c>
       <c r="F54">
         <v>3485</v>
@@ -1934,19 +1934,19 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D55">
-        <v>685</v>
+        <v>2</v>
       </c>
       <c r="E55">
-        <v>1033</v>
+        <v>2</v>
       </c>
       <c r="F55">
         <v>3485</v>
@@ -1963,19 +1963,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D56">
-        <v>348</v>
+        <v>2223</v>
       </c>
       <c r="E56">
-        <v>1033</v>
+        <v>2450</v>
       </c>
       <c r="F56">
         <v>3485</v>
@@ -1992,19 +1992,19 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D57">
-        <v>0</v>
+        <v>190</v>
       </c>
       <c r="E57">
-        <v>0</v>
+        <v>2450</v>
       </c>
       <c r="F57">
         <v>3485</v>
@@ -2017,26 +2017,26 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D58">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="E58">
-        <v>0</v>
+        <v>2450</v>
       </c>
       <c r="F58">
-        <v>2418</v>
+        <v>3485</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2046,26 +2046,26 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>685</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>1033</v>
       </c>
       <c r="F59">
-        <v>2418</v>
+        <v>3485</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2075,26 +2075,26 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D60">
-        <v>1144</v>
+        <v>348</v>
       </c>
       <c r="E60">
-        <v>1503</v>
+        <v>1033</v>
       </c>
       <c r="F60">
-        <v>2418</v>
+        <v>3485</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2104,26 +2104,26 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>2031</v>
+        <v>2030</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D61">
-        <v>339</v>
+        <v>0</v>
       </c>
       <c r="E61">
-        <v>1503</v>
+        <v>0</v>
       </c>
       <c r="F61">
-        <v>2418</v>
+        <v>3485</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2137,19 +2137,19 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D62">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E62">
-        <v>1503</v>
+        <v>0</v>
       </c>
       <c r="F62">
         <v>2418</v>
@@ -2166,19 +2166,19 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D63">
-        <v>685</v>
+        <v>0</v>
       </c>
       <c r="E63">
-        <v>915</v>
+        <v>0</v>
       </c>
       <c r="F63">
         <v>2418</v>
@@ -2195,19 +2195,19 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D64">
-        <v>230</v>
+        <v>1144</v>
       </c>
       <c r="E64">
-        <v>915</v>
+        <v>1503</v>
       </c>
       <c r="F64">
         <v>2418</v>
@@ -2224,19 +2224,19 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D65">
-        <v>0</v>
+        <v>339</v>
       </c>
       <c r="E65">
-        <v>0</v>
+        <v>1503</v>
       </c>
       <c r="F65">
         <v>2418</v>
@@ -2249,26 +2249,26 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D66">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="E66">
-        <v>0</v>
+        <v>1503</v>
       </c>
       <c r="F66">
-        <v>1374</v>
+        <v>2418</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2278,26 +2278,26 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D67">
-        <v>0</v>
+        <v>685</v>
       </c>
       <c r="E67">
-        <v>0</v>
+        <v>915</v>
       </c>
       <c r="F67">
-        <v>1374</v>
+        <v>2418</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2307,26 +2307,26 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D68">
-        <v>11</v>
+        <v>230</v>
       </c>
       <c r="E68">
-        <v>416</v>
+        <v>915</v>
       </c>
       <c r="F68">
-        <v>1374</v>
+        <v>2418</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2336,26 +2336,26 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>2032</v>
+        <v>2031</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D69">
-        <v>384</v>
+        <v>0</v>
       </c>
       <c r="E69">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="F69">
-        <v>1374</v>
+        <v>2418</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2369,19 +2369,19 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D70">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E70">
-        <v>416</v>
+        <v>0</v>
       </c>
       <c r="F70">
         <v>1374</v>
@@ -2398,19 +2398,19 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D71">
-        <v>685</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>958</v>
+        <v>0</v>
       </c>
       <c r="F71">
         <v>1374</v>
@@ -2427,19 +2427,19 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D72">
-        <v>273</v>
+        <v>11</v>
       </c>
       <c r="E72">
-        <v>958</v>
+        <v>416</v>
       </c>
       <c r="F72">
         <v>1374</v>
@@ -2456,19 +2456,19 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D73">
-        <v>0</v>
+        <v>384</v>
       </c>
       <c r="E73">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="F73">
         <v>1374</v>
@@ -2481,26 +2481,26 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D74">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E74">
-        <v>0</v>
+        <v>416</v>
       </c>
       <c r="F74">
-        <v>1058</v>
+        <v>1374</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2510,26 +2510,26 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D75">
-        <v>0</v>
+        <v>685</v>
       </c>
       <c r="E75">
-        <v>0</v>
+        <v>958</v>
       </c>
       <c r="F75">
-        <v>1058</v>
+        <v>1374</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2539,26 +2539,26 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D76">
-        <v>16</v>
+        <v>273</v>
       </c>
       <c r="E76">
-        <v>105</v>
+        <v>958</v>
       </c>
       <c r="F76">
-        <v>1058</v>
+        <v>1374</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2568,26 +2568,26 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>2033</v>
+        <v>2032</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D77">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="E77">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="F77">
-        <v>1058</v>
+        <v>1374</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2601,19 +2601,19 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D78">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E78">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="F78">
         <v>1058</v>
@@ -2630,19 +2630,19 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D79">
-        <v>689</v>
+        <v>0</v>
       </c>
       <c r="E79">
-        <v>953</v>
+        <v>0</v>
       </c>
       <c r="F79">
         <v>1058</v>
@@ -2659,19 +2659,19 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D80">
-        <v>264</v>
+        <v>16</v>
       </c>
       <c r="E80">
-        <v>953</v>
+        <v>105</v>
       </c>
       <c r="F80">
         <v>1058</v>
@@ -2688,19 +2688,19 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D81">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="E81">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F81">
         <v>1058</v>
@@ -2713,26 +2713,26 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D82">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E82">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="F82">
-        <v>1026</v>
+        <v>1058</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -2742,26 +2742,26 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D83">
-        <v>0</v>
+        <v>689</v>
       </c>
       <c r="E83">
-        <v>0</v>
+        <v>953</v>
       </c>
       <c r="F83">
-        <v>1026</v>
+        <v>1058</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -2771,26 +2771,26 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D84">
-        <v>12</v>
+        <v>264</v>
       </c>
       <c r="E84">
-        <v>30</v>
+        <v>953</v>
       </c>
       <c r="F84">
-        <v>1026</v>
+        <v>1058</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -2800,26 +2800,26 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>2034</v>
+        <v>2033</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D85">
         <v>0</v>
       </c>
       <c r="E85">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F85">
-        <v>1026</v>
+        <v>1058</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -2833,19 +2833,19 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D86">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E86">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F86">
         <v>1026</v>
@@ -2862,19 +2862,19 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D87">
-        <v>693</v>
+        <v>0</v>
       </c>
       <c r="E87">
-        <v>996</v>
+        <v>0</v>
       </c>
       <c r="F87">
         <v>1026</v>
@@ -2891,19 +2891,19 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D88">
-        <v>303</v>
+        <v>12</v>
       </c>
       <c r="E88">
-        <v>996</v>
+        <v>30</v>
       </c>
       <c r="F88">
         <v>1026</v>
@@ -2920,19 +2920,19 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D89">
         <v>0</v>
       </c>
       <c r="E89">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F89">
         <v>1026</v>
@@ -2945,26 +2945,26 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D90">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E90">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F90">
-        <v>1001</v>
+        <v>1026</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -2974,26 +2974,26 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D91">
-        <v>0</v>
+        <v>693</v>
       </c>
       <c r="E91">
-        <v>0</v>
+        <v>996</v>
       </c>
       <c r="F91">
-        <v>1001</v>
+        <v>1026</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3003,26 +3003,26 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D92">
-        <v>30</v>
+        <v>303</v>
       </c>
       <c r="E92">
-        <v>52</v>
+        <v>996</v>
       </c>
       <c r="F92">
-        <v>1001</v>
+        <v>1026</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3032,26 +3032,26 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D93">
         <v>0</v>
       </c>
       <c r="E93">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F93">
-        <v>1001</v>
+        <v>1026</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3065,19 +3065,19 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D94">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="E94">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F94">
         <v>1001</v>
@@ -3094,19 +3094,19 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D95">
-        <v>698</v>
+        <v>0</v>
       </c>
       <c r="E95">
-        <v>949</v>
+        <v>0</v>
       </c>
       <c r="F95">
         <v>1001</v>
@@ -3123,19 +3123,19 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D96">
-        <v>251</v>
+        <v>30</v>
       </c>
       <c r="E96">
-        <v>949</v>
+        <v>52</v>
       </c>
       <c r="F96">
         <v>1001</v>
@@ -3152,19 +3152,19 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D97">
         <v>0</v>
       </c>
       <c r="E97">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F97">
         <v>1001</v>
@@ -3177,26 +3177,26 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="F98">
-        <v>889</v>
+        <v>1001</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3206,26 +3206,26 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D99">
-        <v>0</v>
+        <v>698</v>
       </c>
       <c r="E99">
-        <v>0</v>
+        <v>949</v>
       </c>
       <c r="F99">
-        <v>889</v>
+        <v>1001</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3235,26 +3235,26 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D100">
-        <v>14</v>
+        <v>251</v>
       </c>
       <c r="E100">
-        <v>31</v>
+        <v>949</v>
       </c>
       <c r="F100">
-        <v>889</v>
+        <v>1001</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3264,26 +3264,26 @@
     </row>
     <row r="101">
       <c r="A101">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D101">
         <v>0</v>
       </c>
       <c r="E101">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F101">
-        <v>889</v>
+        <v>1001</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3297,19 +3297,19 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D102">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E102">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F102">
         <v>889</v>
@@ -3326,19 +3326,19 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D103">
-        <v>702</v>
+        <v>0</v>
       </c>
       <c r="E103">
-        <v>858</v>
+        <v>0</v>
       </c>
       <c r="F103">
         <v>889</v>
@@ -3355,19 +3355,19 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D104">
-        <v>156</v>
+        <v>14</v>
       </c>
       <c r="E104">
-        <v>858</v>
+        <v>31</v>
       </c>
       <c r="F104">
         <v>889</v>
@@ -3384,19 +3384,19 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D105">
         <v>0</v>
       </c>
       <c r="E105">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F105">
         <v>889</v>
@@ -3409,26 +3409,26 @@
     </row>
     <row r="106">
       <c r="A106">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D106">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="E106">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F106">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -3438,26 +3438,26 @@
     </row>
     <row r="107">
       <c r="A107">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D107">
-        <v>0</v>
+        <v>702</v>
       </c>
       <c r="E107">
-        <v>0</v>
+        <v>858</v>
       </c>
       <c r="F107">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3467,26 +3467,26 @@
     </row>
     <row r="108">
       <c r="A108">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D108">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="E108">
-        <v>32</v>
+        <v>858</v>
       </c>
       <c r="F108">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -3496,26 +3496,26 @@
     </row>
     <row r="109">
       <c r="A109">
-        <v>2037</v>
+        <v>2036</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D109">
         <v>0</v>
       </c>
       <c r="E109">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F109">
-        <v>894</v>
+        <v>889</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3529,19 +3529,19 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D110">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="E110">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="F110">
         <v>894</v>
@@ -3558,19 +3558,19 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D111">
-        <v>706</v>
+        <v>0</v>
       </c>
       <c r="E111">
-        <v>862</v>
+        <v>0</v>
       </c>
       <c r="F111">
         <v>894</v>
@@ -3587,19 +3587,19 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D112">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="E112">
-        <v>862</v>
+        <v>32</v>
       </c>
       <c r="F112">
         <v>894</v>
@@ -3616,19 +3616,19 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D113">
         <v>0</v>
       </c>
       <c r="E113">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F113">
         <v>894</v>
@@ -3641,26 +3641,26 @@
     </row>
     <row r="114">
       <c r="A114">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D114">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="E114">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F114">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -3670,26 +3670,26 @@
     </row>
     <row r="115">
       <c r="A115">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D115">
-        <v>0</v>
+        <v>706</v>
       </c>
       <c r="E115">
-        <v>0</v>
+        <v>862</v>
       </c>
       <c r="F115">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -3699,26 +3699,26 @@
     </row>
     <row r="116">
       <c r="A116">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D116">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="E116">
-        <v>29</v>
+        <v>862</v>
       </c>
       <c r="F116">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -3728,26 +3728,26 @@
     </row>
     <row r="117">
       <c r="A117">
-        <v>2038</v>
+        <v>2037</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D117">
         <v>0</v>
       </c>
       <c r="E117">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F117">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -3761,19 +3761,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D118">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E118">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="F118">
         <v>896</v>
@@ -3790,19 +3790,19 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D119">
-        <v>711</v>
+        <v>0</v>
       </c>
       <c r="E119">
-        <v>867</v>
+        <v>0</v>
       </c>
       <c r="F119">
         <v>896</v>
@@ -3819,19 +3819,19 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D120">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="E120">
-        <v>867</v>
+        <v>29</v>
       </c>
       <c r="F120">
         <v>896</v>
@@ -3848,19 +3848,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D121">
         <v>0</v>
       </c>
       <c r="E121">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F121">
         <v>896</v>
@@ -3873,26 +3873,26 @@
     </row>
     <row r="122">
       <c r="A122">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D122">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E122">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F122">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -3902,26 +3902,26 @@
     </row>
     <row r="123">
       <c r="A123">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D123">
-        <v>0</v>
+        <v>711</v>
       </c>
       <c r="E123">
-        <v>0</v>
+        <v>867</v>
       </c>
       <c r="F123">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -3931,26 +3931,26 @@
     </row>
     <row r="124">
       <c r="A124">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D124">
-        <v>13</v>
+        <v>156</v>
       </c>
       <c r="E124">
-        <v>31</v>
+        <v>867</v>
       </c>
       <c r="F124">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -3960,26 +3960,26 @@
     </row>
     <row r="125">
       <c r="A125">
-        <v>2039</v>
+        <v>2038</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D125">
         <v>0</v>
       </c>
       <c r="E125">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F125">
-        <v>903</v>
+        <v>896</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -3993,19 +3993,19 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D126">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="E126">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="F126">
         <v>903</v>
@@ -4022,19 +4022,19 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D127">
-        <v>716</v>
+        <v>0</v>
       </c>
       <c r="E127">
-        <v>872</v>
+        <v>0</v>
       </c>
       <c r="F127">
         <v>903</v>
@@ -4051,19 +4051,19 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D128">
-        <v>156</v>
+        <v>13</v>
       </c>
       <c r="E128">
-        <v>872</v>
+        <v>31</v>
       </c>
       <c r="F128">
         <v>903</v>
@@ -4080,19 +4080,19 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D129">
         <v>0</v>
       </c>
       <c r="E129">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F129">
         <v>903</v>
@@ -4105,26 +4105,26 @@
     </row>
     <row r="130">
       <c r="A130">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D130">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="E130">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F130">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -4134,26 +4134,26 @@
     </row>
     <row r="131">
       <c r="A131">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D131">
-        <v>0</v>
+        <v>716</v>
       </c>
       <c r="E131">
-        <v>0</v>
+        <v>872</v>
       </c>
       <c r="F131">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -4163,26 +4163,26 @@
     </row>
     <row r="132">
       <c r="A132">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D132">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="E132">
-        <v>25</v>
+        <v>872</v>
       </c>
       <c r="F132">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -4192,26 +4192,26 @@
     </row>
     <row r="133">
       <c r="A133">
-        <v>2040</v>
+        <v>2039</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D133">
         <v>0</v>
       </c>
       <c r="E133">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F133">
-        <v>901</v>
+        <v>903</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4225,19 +4225,19 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D134">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="E134">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="F134">
         <v>901</v>
@@ -4254,19 +4254,19 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D135">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="E135">
-        <v>876</v>
+        <v>0</v>
       </c>
       <c r="F135">
         <v>901</v>
@@ -4283,19 +4283,19 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D136">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="E136">
-        <v>876</v>
+        <v>25</v>
       </c>
       <c r="F136">
         <v>901</v>
@@ -4312,19 +4312,19 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D137">
         <v>0</v>
       </c>
       <c r="E137">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F137">
         <v>901</v>
@@ -4337,26 +4337,26 @@
     </row>
     <row r="138">
       <c r="A138">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D138">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="E138">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F138">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -4366,26 +4366,26 @@
     </row>
     <row r="139">
       <c r="A139">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D139">
-        <v>0</v>
+        <v>720</v>
       </c>
       <c r="E139">
-        <v>0</v>
+        <v>876</v>
       </c>
       <c r="F139">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -4395,26 +4395,26 @@
     </row>
     <row r="140">
       <c r="A140">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D140">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="E140">
-        <v>27</v>
+        <v>876</v>
       </c>
       <c r="F140">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -4424,26 +4424,26 @@
     </row>
     <row r="141">
       <c r="A141">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D141">
         <v>0</v>
       </c>
       <c r="E141">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F141">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -4457,19 +4457,19 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D142">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E142">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="F142">
         <v>908</v>
@@ -4486,19 +4486,19 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D143">
-        <v>725</v>
+        <v>0</v>
       </c>
       <c r="E143">
-        <v>881</v>
+        <v>0</v>
       </c>
       <c r="F143">
         <v>908</v>
@@ -4515,19 +4515,19 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D144">
-        <v>156</v>
+        <v>11</v>
       </c>
       <c r="E144">
-        <v>881</v>
+        <v>27</v>
       </c>
       <c r="F144">
         <v>908</v>
@@ -4544,19 +4544,19 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D145">
         <v>0</v>
       </c>
       <c r="E145">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F145">
         <v>908</v>
@@ -4569,26 +4569,26 @@
     </row>
     <row r="146">
       <c r="A146">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D146">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="E146">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F146">
-        <v>760</v>
+        <v>908</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -4598,26 +4598,26 @@
     </row>
     <row r="147">
       <c r="A147">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D147">
-        <v>0</v>
+        <v>725</v>
       </c>
       <c r="E147">
-        <v>0</v>
+        <v>881</v>
       </c>
       <c r="F147">
-        <v>760</v>
+        <v>908</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -4627,26 +4627,26 @@
     </row>
     <row r="148">
       <c r="A148">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D148">
-        <v>11</v>
+        <v>156</v>
       </c>
       <c r="E148">
-        <v>30</v>
+        <v>881</v>
       </c>
       <c r="F148">
-        <v>760</v>
+        <v>908</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -4656,26 +4656,26 @@
     </row>
     <row r="149">
       <c r="A149">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D149">
         <v>0</v>
       </c>
       <c r="E149">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F149">
-        <v>760</v>
+        <v>908</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -4689,19 +4689,19 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D150">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E150">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="F150">
         <v>760</v>
@@ -4718,19 +4718,19 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D151">
-        <v>730</v>
+        <v>0</v>
       </c>
       <c r="E151">
-        <v>730</v>
+        <v>0</v>
       </c>
       <c r="F151">
         <v>760</v>
@@ -4747,19 +4747,19 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D152">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E152">
-        <v>730</v>
+        <v>30</v>
       </c>
       <c r="F152">
         <v>760</v>
@@ -4776,19 +4776,19 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D153">
         <v>0</v>
       </c>
       <c r="E153">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F153">
         <v>760</v>
@@ -4801,26 +4801,26 @@
     </row>
     <row r="154">
       <c r="A154">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D154">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="E154">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F154">
-        <v>808</v>
+        <v>760</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -4830,26 +4830,26 @@
     </row>
     <row r="155">
       <c r="A155">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D155">
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="E155">
-        <v>0</v>
+        <v>730</v>
       </c>
       <c r="F155">
-        <v>808</v>
+        <v>760</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -4859,26 +4859,26 @@
     </row>
     <row r="156">
       <c r="A156">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D156">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E156">
-        <v>73</v>
+        <v>730</v>
       </c>
       <c r="F156">
-        <v>808</v>
+        <v>760</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -4888,26 +4888,26 @@
     </row>
     <row r="157">
       <c r="A157">
-        <v>2043</v>
+        <v>2042</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D157">
         <v>0</v>
       </c>
       <c r="E157">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="F157">
-        <v>808</v>
+        <v>760</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -4921,19 +4921,19 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D158">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="E158">
-        <v>73</v>
+        <v>0</v>
       </c>
       <c r="F158">
         <v>808</v>
@@ -4950,19 +4950,19 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D159">
-        <v>735</v>
+        <v>0</v>
       </c>
       <c r="E159">
-        <v>735</v>
+        <v>0</v>
       </c>
       <c r="F159">
         <v>808</v>
@@ -4979,19 +4979,19 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D160">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="E160">
-        <v>735</v>
+        <v>73</v>
       </c>
       <c r="F160">
         <v>808</v>
@@ -5008,19 +5008,19 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D161">
         <v>0</v>
       </c>
       <c r="E161">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="F161">
         <v>808</v>
@@ -5033,26 +5033,26 @@
     </row>
     <row r="162">
       <c r="A162">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D162">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="E162">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="F162">
-        <v>834</v>
+        <v>808</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -5062,26 +5062,26 @@
     </row>
     <row r="163">
       <c r="A163">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D163">
-        <v>0</v>
+        <v>735</v>
       </c>
       <c r="E163">
-        <v>0</v>
+        <v>735</v>
       </c>
       <c r="F163">
-        <v>834</v>
+        <v>808</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -5091,26 +5091,26 @@
     </row>
     <row r="164">
       <c r="A164">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D164">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="E164">
-        <v>94</v>
+        <v>735</v>
       </c>
       <c r="F164">
-        <v>834</v>
+        <v>808</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -5120,26 +5120,26 @@
     </row>
     <row r="165">
       <c r="A165">
-        <v>2044</v>
+        <v>2043</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D165">
         <v>0</v>
       </c>
       <c r="E165">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="F165">
-        <v>834</v>
+        <v>808</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -5153,19 +5153,19 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D166">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E166">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="F166">
         <v>834</v>
@@ -5182,19 +5182,19 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D167">
-        <v>740</v>
+        <v>0</v>
       </c>
       <c r="E167">
-        <v>740</v>
+        <v>0</v>
       </c>
       <c r="F167">
         <v>834</v>
@@ -5211,19 +5211,19 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D168">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="E168">
-        <v>740</v>
+        <v>94</v>
       </c>
       <c r="F168">
         <v>834</v>
@@ -5240,19 +5240,19 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D169">
         <v>0</v>
       </c>
       <c r="E169">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="F169">
         <v>834</v>
@@ -5265,26 +5265,26 @@
     </row>
     <row r="170">
       <c r="A170">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D170">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E170">
-        <v>0</v>
+        <v>94</v>
       </c>
       <c r="F170">
-        <v>773</v>
+        <v>834</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -5294,26 +5294,26 @@
     </row>
     <row r="171">
       <c r="A171">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D171">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="E171">
-        <v>0</v>
+        <v>740</v>
       </c>
       <c r="F171">
-        <v>773</v>
+        <v>834</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -5323,26 +5323,26 @@
     </row>
     <row r="172">
       <c r="A172">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D172">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E172">
-        <v>28</v>
+        <v>740</v>
       </c>
       <c r="F172">
-        <v>773</v>
+        <v>834</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -5352,26 +5352,26 @@
     </row>
     <row r="173">
       <c r="A173">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D173">
         <v>0</v>
       </c>
       <c r="E173">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F173">
-        <v>773</v>
+        <v>834</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -5385,19 +5385,19 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D174">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E174">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F174">
         <v>773</v>
@@ -5414,19 +5414,19 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D175">
-        <v>745</v>
+        <v>0</v>
       </c>
       <c r="E175">
-        <v>745</v>
+        <v>0</v>
       </c>
       <c r="F175">
         <v>773</v>
@@ -5443,19 +5443,19 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D176">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E176">
-        <v>745</v>
+        <v>28</v>
       </c>
       <c r="F176">
         <v>773</v>
@@ -5472,19 +5472,19 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D177">
         <v>0</v>
       </c>
       <c r="E177">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F177">
         <v>773</v>
@@ -5497,26 +5497,26 @@
     </row>
     <row r="178">
       <c r="A178">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D178">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E178">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F178">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -5526,26 +5526,26 @@
     </row>
     <row r="179">
       <c r="A179">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D179">
-        <v>0</v>
+        <v>745</v>
       </c>
       <c r="E179">
-        <v>0</v>
+        <v>745</v>
       </c>
       <c r="F179">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -5555,26 +5555,26 @@
     </row>
     <row r="180">
       <c r="A180">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D180">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E180">
-        <v>28</v>
+        <v>745</v>
       </c>
       <c r="F180">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -5584,26 +5584,26 @@
     </row>
     <row r="181">
       <c r="A181">
-        <v>2046</v>
+        <v>2045</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D181">
         <v>0</v>
       </c>
       <c r="E181">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F181">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -5617,19 +5617,19 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D182">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="E182">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F182">
         <v>779</v>
@@ -5646,19 +5646,19 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D183">
-        <v>751</v>
+        <v>0</v>
       </c>
       <c r="E183">
-        <v>751</v>
+        <v>0</v>
       </c>
       <c r="F183">
         <v>779</v>
@@ -5675,19 +5675,19 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D184">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E184">
-        <v>751</v>
+        <v>28</v>
       </c>
       <c r="F184">
         <v>779</v>
@@ -5704,19 +5704,19 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D185">
         <v>0</v>
       </c>
       <c r="E185">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F185">
         <v>779</v>
@@ -5729,26 +5729,26 @@
     </row>
     <row r="186">
       <c r="A186">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D186">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="E186">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F186">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -5758,26 +5758,26 @@
     </row>
     <row r="187">
       <c r="A187">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D187">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="E187">
-        <v>0</v>
+        <v>751</v>
       </c>
       <c r="F187">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -5787,26 +5787,26 @@
     </row>
     <row r="188">
       <c r="A188">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D188">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E188">
-        <v>8</v>
+        <v>751</v>
       </c>
       <c r="F188">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -5816,26 +5816,26 @@
     </row>
     <row r="189">
       <c r="A189">
-        <v>2047</v>
+        <v>2046</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D189">
         <v>0</v>
       </c>
       <c r="E189">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F189">
-        <v>765</v>
+        <v>779</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -5849,19 +5849,19 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D190">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E190">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F190">
         <v>765</v>
@@ -5878,19 +5878,19 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D191">
-        <v>757</v>
+        <v>0</v>
       </c>
       <c r="E191">
-        <v>757</v>
+        <v>0</v>
       </c>
       <c r="F191">
         <v>765</v>
@@ -5907,19 +5907,19 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D192">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E192">
-        <v>757</v>
+        <v>8</v>
       </c>
       <c r="F192">
         <v>765</v>
@@ -5936,19 +5936,19 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D193">
         <v>0</v>
       </c>
       <c r="E193">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F193">
         <v>765</v>
@@ -5961,26 +5961,26 @@
     </row>
     <row r="194">
       <c r="A194">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D194">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E194">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F194">
-        <v>444</v>
+        <v>765</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -5990,26 +5990,26 @@
     </row>
     <row r="195">
       <c r="A195">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D195">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="E195">
-        <v>0</v>
+        <v>757</v>
       </c>
       <c r="F195">
-        <v>444</v>
+        <v>765</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -6019,26 +6019,26 @@
     </row>
     <row r="196">
       <c r="A196">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D196">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E196">
-        <v>8</v>
+        <v>757</v>
       </c>
       <c r="F196">
-        <v>444</v>
+        <v>765</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -6048,26 +6048,26 @@
     </row>
     <row r="197">
       <c r="A197">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D197">
         <v>0</v>
       </c>
       <c r="E197">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F197">
-        <v>444</v>
+        <v>765</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -6081,19 +6081,19 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D198">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E198">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F198">
         <v>444</v>
@@ -6110,19 +6110,19 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D199">
-        <v>436</v>
+        <v>0</v>
       </c>
       <c r="E199">
-        <v>436</v>
+        <v>0</v>
       </c>
       <c r="F199">
         <v>444</v>
@@ -6139,19 +6139,19 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D200">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E200">
-        <v>436</v>
+        <v>8</v>
       </c>
       <c r="F200">
         <v>444</v>
@@ -6168,19 +6168,19 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D201">
         <v>0</v>
       </c>
       <c r="E201">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F201">
         <v>444</v>
@@ -6193,26 +6193,26 @@
     </row>
     <row r="202">
       <c r="A202">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D202">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E202">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F202">
-        <v>8</v>
+        <v>444</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -6222,26 +6222,26 @@
     </row>
     <row r="203">
       <c r="A203">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D203">
-        <v>0</v>
+        <v>436</v>
       </c>
       <c r="E203">
-        <v>0</v>
+        <v>436</v>
       </c>
       <c r="F203">
-        <v>8</v>
+        <v>444</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -6251,26 +6251,26 @@
     </row>
     <row r="204">
       <c r="A204">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D204">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E204">
-        <v>8</v>
+        <v>436</v>
       </c>
       <c r="F204">
-        <v>8</v>
+        <v>444</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -6280,26 +6280,26 @@
     </row>
     <row r="205">
       <c r="A205">
-        <v>2049</v>
+        <v>2048</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D205">
         <v>0</v>
       </c>
       <c r="E205">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F205">
-        <v>8</v>
+        <v>444</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -6313,19 +6313,19 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D206">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E206">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F206">
         <v>8</v>
@@ -6342,12 +6342,12 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D207">
@@ -6371,19 +6371,19 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D208">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E208">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F208">
         <v>8</v>
@@ -6400,19 +6400,19 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D209">
         <v>0</v>
       </c>
       <c r="E209">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F209">
         <v>8</v>
@@ -6425,23 +6425,23 @@
     </row>
     <row r="210">
       <c r="A210">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D210">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E210">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F210">
         <v>8</v>
@@ -6454,16 +6454,16 @@
     </row>
     <row r="211">
       <c r="A211">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D211">
@@ -6483,23 +6483,23 @@
     </row>
     <row r="212">
       <c r="A212">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E212">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F212">
         <v>8</v>
@@ -6512,23 +6512,23 @@
     </row>
     <row r="213">
       <c r="A213">
-        <v>2050</v>
+        <v>2049</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D213">
         <v>0</v>
       </c>
       <c r="E213">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F213">
         <v>8</v>
@@ -6545,19 +6545,19 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D214">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E214">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F214">
         <v>8</v>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D215">
@@ -6603,19 +6603,19 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D216">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E216">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F216">
         <v>8</v>
@@ -6632,19 +6632,19 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D217">
         <v>0</v>
       </c>
       <c r="E217">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F217">
         <v>8</v>
@@ -6657,23 +6657,23 @@
     </row>
     <row r="218">
       <c r="A218">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D218">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E218">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F218">
         <v>8</v>
@@ -6686,16 +6686,16 @@
     </row>
     <row r="219">
       <c r="A219">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D219">
@@ -6715,23 +6715,23 @@
     </row>
     <row r="220">
       <c r="A220">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D220">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E220">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F220">
         <v>8</v>
@@ -6744,23 +6744,23 @@
     </row>
     <row r="221">
       <c r="A221">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D221">
         <v>0</v>
       </c>
       <c r="E221">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F221">
         <v>8</v>
@@ -6777,19 +6777,19 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D222">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E222">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F222">
         <v>8</v>
@@ -6806,12 +6806,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D223">
@@ -6835,19 +6835,19 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D224">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E224">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F224">
         <v>8</v>
@@ -6864,19 +6864,19 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D225">
         <v>0</v>
       </c>
       <c r="E225">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F225">
         <v>8</v>
@@ -6889,23 +6889,23 @@
     </row>
     <row r="226">
       <c r="A226">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D226">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E226">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F226">
         <v>8</v>
@@ -6918,16 +6918,16 @@
     </row>
     <row r="227">
       <c r="A227">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D227">
@@ -6947,23 +6947,23 @@
     </row>
     <row r="228">
       <c r="A228">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D228">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E228">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F228">
         <v>8</v>
@@ -6976,23 +6976,23 @@
     </row>
     <row r="229">
       <c r="A229">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D229">
         <v>0</v>
       </c>
       <c r="E229">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F229">
         <v>8</v>
@@ -7009,19 +7009,19 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D230">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E230">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F230">
         <v>8</v>
@@ -7038,12 +7038,12 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D231">
@@ -7067,19 +7067,19 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E232">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F232">
         <v>8</v>
@@ -7096,19 +7096,19 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D233">
         <v>0</v>
       </c>
       <c r="E233">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F233">
         <v>8</v>
@@ -7121,23 +7121,23 @@
     </row>
     <row r="234">
       <c r="A234">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D234">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E234">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F234">
         <v>8</v>
@@ -7150,16 +7150,16 @@
     </row>
     <row r="235">
       <c r="A235">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D235">
@@ -7179,23 +7179,23 @@
     </row>
     <row r="236">
       <c r="A236">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D236">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E236">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F236">
         <v>8</v>
@@ -7208,23 +7208,23 @@
     </row>
     <row r="237">
       <c r="A237">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D237">
         <v>0</v>
       </c>
       <c r="E237">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F237">
         <v>8</v>
@@ -7241,19 +7241,19 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D238">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E238">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F238">
         <v>8</v>
@@ -7270,12 +7270,12 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D239">
@@ -7299,19 +7299,19 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D240">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E240">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F240">
         <v>8</v>
@@ -7328,19 +7328,19 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D241">
         <v>0</v>
       </c>
       <c r="E241">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F241">
         <v>8</v>
@@ -7353,23 +7353,23 @@
     </row>
     <row r="242">
       <c r="A242">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D242">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E242">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F242">
         <v>8</v>
@@ -7382,16 +7382,16 @@
     </row>
     <row r="243">
       <c r="A243">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D243">
@@ -7411,23 +7411,23 @@
     </row>
     <row r="244">
       <c r="A244">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D244">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E244">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F244">
         <v>8</v>
@@ -7440,23 +7440,23 @@
     </row>
     <row r="245">
       <c r="A245">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D245">
         <v>0</v>
       </c>
       <c r="E245">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F245">
         <v>8</v>
@@ -7473,19 +7473,19 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D246">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E246">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F246">
         <v>8</v>
@@ -7502,12 +7502,12 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D247">
@@ -7531,19 +7531,19 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D248">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E248">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F248">
         <v>8</v>
@@ -7560,19 +7560,19 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D249">
         <v>0</v>
       </c>
       <c r="E249">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F249">
         <v>8</v>
@@ -7585,26 +7585,26 @@
     </row>
     <row r="250">
       <c r="A250">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D250">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E250">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F250">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -7614,16 +7614,16 @@
     </row>
     <row r="251">
       <c r="A251">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D251">
@@ -7633,7 +7633,7 @@
         <v>0</v>
       </c>
       <c r="F251">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -7643,26 +7643,26 @@
     </row>
     <row r="252">
       <c r="A252">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D252">
         <v>0</v>
       </c>
       <c r="E252">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F252">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -7672,26 +7672,26 @@
     </row>
     <row r="253">
       <c r="A253">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D253">
         <v>0</v>
       </c>
       <c r="E253">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F253">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -7705,19 +7705,19 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D254">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E254">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F254">
         <v>7</v>
@@ -7734,12 +7734,12 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D255">
@@ -7763,19 +7763,19 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D256">
         <v>0</v>
       </c>
       <c r="E256">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F256">
         <v>7</v>
@@ -7792,19 +7792,19 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D257">
         <v>0</v>
       </c>
       <c r="E257">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F257">
         <v>7</v>
@@ -7817,26 +7817,26 @@
     </row>
     <row r="258">
       <c r="A258">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Energía Eléctrica</t>
+          <t>Oro y Plata</t>
         </is>
       </c>
       <c r="D258">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="E258">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F258">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
@@ -7846,16 +7846,16 @@
     </row>
     <row r="259">
       <c r="A259">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>Infraestructura</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Puerto</t>
+          <t>Midstream</t>
         </is>
       </c>
       <c r="D259">
@@ -7865,7 +7865,7 @@
         <v>0</v>
       </c>
       <c r="F259">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
@@ -7875,26 +7875,26 @@
     </row>
     <row r="260">
       <c r="A260">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Petróleo y Gas</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Cobre</t>
+          <t>Upstream</t>
         </is>
       </c>
       <c r="D260">
         <v>0</v>
       </c>
       <c r="E260">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F260">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -7904,26 +7904,26 @@
     </row>
     <row r="261">
       <c r="A261">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Litio</t>
+          <t>Siderurgia</t>
         </is>
       </c>
       <c r="D261">
         <v>0</v>
       </c>
       <c r="E261">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F261">
-        <v>44</v>
+        <v>7</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -7937,19 +7937,19 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>Minería</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Oro y Plata</t>
+          <t>Energía Eléctrica</t>
         </is>
       </c>
       <c r="D262">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="E262">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="F262">
         <v>44</v>
@@ -7966,12 +7966,12 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Infraestructura</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Midstream</t>
+          <t>Puerto</t>
         </is>
       </c>
       <c r="D263">
@@ -7995,19 +7995,19 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>Petróleo y Gas</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Upstream</t>
+          <t>Cobre</t>
         </is>
       </c>
       <c r="D264">
         <v>0</v>
       </c>
       <c r="E264">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F264">
         <v>44</v>
@@ -8024,24 +8024,140 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Minería</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Siderurgia</t>
+          <t>Litio</t>
         </is>
       </c>
       <c r="D265">
         <v>0</v>
       </c>
       <c r="E265">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="F265">
         <v>44</v>
       </c>
       <c r="G265" t="inlineStr">
+        <is>
+          <t>https://www.argentina.gob.ar/economia/rigi</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266">
+        <v>2056</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Minería</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Oro y Plata</t>
+        </is>
+      </c>
+      <c r="D266">
+        <v>44</v>
+      </c>
+      <c r="E266">
+        <v>44</v>
+      </c>
+      <c r="F266">
+        <v>44</v>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>https://www.argentina.gob.ar/economia/rigi</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267">
+        <v>2056</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Petróleo y Gas</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Midstream</t>
+        </is>
+      </c>
+      <c r="D267">
+        <v>0</v>
+      </c>
+      <c r="E267">
+        <v>0</v>
+      </c>
+      <c r="F267">
+        <v>44</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>https://www.argentina.gob.ar/economia/rigi</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268">
+        <v>2056</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Petróleo y Gas</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Upstream</t>
+        </is>
+      </c>
+      <c r="D268">
+        <v>0</v>
+      </c>
+      <c r="E268">
+        <v>0</v>
+      </c>
+      <c r="F268">
+        <v>44</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>https://www.argentina.gob.ar/economia/rigi</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269">
+        <v>2056</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Siderurgia</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Siderurgia</t>
+        </is>
+      </c>
+      <c r="D269">
+        <v>0</v>
+      </c>
+      <c r="E269">
+        <v>0</v>
+      </c>
+      <c r="F269">
+        <v>44</v>
+      </c>
+      <c r="G269" t="inlineStr">
         <is>
           <t>https://www.argentina.gob.ar/economia/rigi</t>
         </is>

--- a/downloads/planes_inversion.xlsx
+++ b/downloads/planes_inversion.xlsx
@@ -412,7 +412,7 @@
         <v>37</v>
       </c>
       <c r="F2">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -441,7 +441,7 @@
         <v>0</v>
       </c>
       <c r="F3">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -464,13 +464,13 @@
         </is>
       </c>
       <c r="D4">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="E4">
-        <v>527</v>
+        <v>542</v>
       </c>
       <c r="F4">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -496,10 +496,10 @@
         <v>374</v>
       </c>
       <c r="E5">
-        <v>527</v>
+        <v>542</v>
       </c>
       <c r="F5">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -525,10 +525,10 @@
         <v>44</v>
       </c>
       <c r="E6">
-        <v>527</v>
+        <v>542</v>
       </c>
       <c r="F6">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -554,10 +554,10 @@
         <v>34</v>
       </c>
       <c r="E7">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F7">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -580,13 +580,13 @@
         </is>
       </c>
       <c r="D8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F8">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -615,7 +615,7 @@
         <v>0</v>
       </c>
       <c r="F9">
-        <v>612</v>
+        <v>628</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -644,7 +644,7 @@
         <v>252</v>
       </c>
       <c r="F10">
-        <v>3701</v>
+        <v>4172</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -673,7 +673,7 @@
         <v>92</v>
       </c>
       <c r="F11">
-        <v>3701</v>
+        <v>4172</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="D12">
-        <v>419</v>
+        <v>440</v>
       </c>
       <c r="E12">
-        <v>1473</v>
+        <v>1493</v>
       </c>
       <c r="F12">
-        <v>3701</v>
+        <v>4172</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -728,10 +728,10 @@
         <v>948</v>
       </c>
       <c r="E13">
-        <v>1473</v>
+        <v>1493</v>
       </c>
       <c r="F13">
-        <v>3701</v>
+        <v>4172</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -757,10 +757,10 @@
         <v>105</v>
       </c>
       <c r="E14">
-        <v>1473</v>
+        <v>1493</v>
       </c>
       <c r="F14">
-        <v>3701</v>
+        <v>4172</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -786,10 +786,10 @@
         <v>1574</v>
       </c>
       <c r="E15">
-        <v>1802</v>
+        <v>2253</v>
       </c>
       <c r="F15">
-        <v>3701</v>
+        <v>4172</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -812,13 +812,13 @@
         </is>
       </c>
       <c r="D16">
-        <v>228</v>
+        <v>679</v>
       </c>
       <c r="E16">
-        <v>1802</v>
+        <v>2253</v>
       </c>
       <c r="F16">
-        <v>3701</v>
+        <v>4172</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -847,7 +847,7 @@
         <v>82</v>
       </c>
       <c r="F17">
-        <v>3701</v>
+        <v>4172</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>162</v>
       </c>
       <c r="F18">
-        <v>6196</v>
+        <v>7654</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>74</v>
       </c>
       <c r="F19">
-        <v>6196</v>
+        <v>7654</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="D20">
-        <v>962</v>
+        <v>1013</v>
       </c>
       <c r="E20">
-        <v>2579</v>
+        <v>2630</v>
       </c>
       <c r="F20">
-        <v>6196</v>
+        <v>7654</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -960,10 +960,10 @@
         <v>1358</v>
       </c>
       <c r="E21">
-        <v>2579</v>
+        <v>2630</v>
       </c>
       <c r="F21">
-        <v>6196</v>
+        <v>7654</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -989,10 +989,10 @@
         <v>259</v>
       </c>
       <c r="E22">
-        <v>2579</v>
+        <v>2630</v>
       </c>
       <c r="F22">
-        <v>6196</v>
+        <v>7654</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1018,10 +1018,10 @@
         <v>527</v>
       </c>
       <c r="E23">
-        <v>3251</v>
+        <v>4658</v>
       </c>
       <c r="F23">
-        <v>6196</v>
+        <v>7654</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1047,10 +1047,10 @@
         <v>2348</v>
       </c>
       <c r="E24">
-        <v>3251</v>
+        <v>4658</v>
       </c>
       <c r="F24">
-        <v>6196</v>
+        <v>7654</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1073,13 +1073,13 @@
         </is>
       </c>
       <c r="D25">
-        <v>376</v>
+        <v>1783</v>
       </c>
       <c r="E25">
-        <v>3251</v>
+        <v>4658</v>
       </c>
       <c r="F25">
-        <v>6196</v>
+        <v>7654</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>130</v>
       </c>
       <c r="F26">
-        <v>6196</v>
+        <v>7654</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
         <v>36</v>
       </c>
       <c r="F27">
-        <v>6251</v>
+        <v>7810</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1166,7 +1166,7 @@
         <v>64</v>
       </c>
       <c r="F28">
-        <v>6251</v>
+        <v>7810</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1189,13 +1189,13 @@
         </is>
       </c>
       <c r="D29">
-        <v>2362</v>
+        <v>2474</v>
       </c>
       <c r="E29">
-        <v>3875</v>
+        <v>3987</v>
       </c>
       <c r="F29">
-        <v>6251</v>
+        <v>7810</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1221,10 +1221,10 @@
         <v>1141</v>
       </c>
       <c r="E30">
-        <v>3875</v>
+        <v>3987</v>
       </c>
       <c r="F30">
-        <v>6251</v>
+        <v>7810</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         <v>372</v>
       </c>
       <c r="E31">
-        <v>3875</v>
+        <v>3987</v>
       </c>
       <c r="F31">
-        <v>6251</v>
+        <v>7810</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1279,10 +1279,10 @@
         <v>578</v>
       </c>
       <c r="E32">
-        <v>2210</v>
+        <v>3657</v>
       </c>
       <c r="F32">
-        <v>6251</v>
+        <v>7810</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1308,10 +1308,10 @@
         <v>1090</v>
       </c>
       <c r="E33">
-        <v>2210</v>
+        <v>3657</v>
       </c>
       <c r="F33">
-        <v>6251</v>
+        <v>7810</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="D34">
-        <v>542</v>
+        <v>1989</v>
       </c>
       <c r="E34">
-        <v>2210</v>
+        <v>3657</v>
       </c>
       <c r="F34">
-        <v>6251</v>
+        <v>7810</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1369,7 +1369,7 @@
         <v>66</v>
       </c>
       <c r="F35">
-        <v>6251</v>
+        <v>7810</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1398,7 +1398,7 @@
         <v>0</v>
       </c>
       <c r="F36">
-        <v>6644</v>
+        <v>8727</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>24</v>
       </c>
       <c r="F37">
-        <v>6644</v>
+        <v>8727</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1450,13 +1450,13 @@
         </is>
       </c>
       <c r="D38">
-        <v>2999</v>
+        <v>3730</v>
       </c>
       <c r="E38">
-        <v>4128</v>
+        <v>4859</v>
       </c>
       <c r="F38">
-        <v>6644</v>
+        <v>8727</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1482,10 +1482,10 @@
         <v>749</v>
       </c>
       <c r="E39">
-        <v>4128</v>
+        <v>4859</v>
       </c>
       <c r="F39">
-        <v>6644</v>
+        <v>8727</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1511,10 +1511,10 @@
         <v>380</v>
       </c>
       <c r="E40">
-        <v>4128</v>
+        <v>4859</v>
       </c>
       <c r="F40">
-        <v>6644</v>
+        <v>8727</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1540,10 +1540,10 @@
         <v>1175</v>
       </c>
       <c r="E41">
-        <v>2484</v>
+        <v>3836</v>
       </c>
       <c r="F41">
-        <v>6644</v>
+        <v>8727</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -1569,10 +1569,10 @@
         <v>818</v>
       </c>
       <c r="E42">
-        <v>2484</v>
+        <v>3836</v>
       </c>
       <c r="F42">
-        <v>6644</v>
+        <v>8727</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="D43">
-        <v>491</v>
+        <v>1843</v>
       </c>
       <c r="E43">
-        <v>2484</v>
+        <v>3836</v>
       </c>
       <c r="F43">
-        <v>6644</v>
+        <v>8727</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -1630,7 +1630,7 @@
         <v>8</v>
       </c>
       <c r="F44">
-        <v>6644</v>
+        <v>8727</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -1659,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="F45">
-        <v>4665</v>
+        <v>6488</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -1688,7 +1688,7 @@
         <v>21</v>
       </c>
       <c r="F46">
-        <v>4665</v>
+        <v>6488</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -1711,13 +1711,13 @@
         </is>
       </c>
       <c r="D47">
-        <v>2843</v>
+        <v>3531</v>
       </c>
       <c r="E47">
-        <v>3278</v>
+        <v>3966</v>
       </c>
       <c r="F47">
-        <v>4665</v>
+        <v>6488</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -1743,10 +1743,10 @@
         <v>229</v>
       </c>
       <c r="E48">
-        <v>3278</v>
+        <v>3966</v>
       </c>
       <c r="F48">
-        <v>4665</v>
+        <v>6488</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -1772,10 +1772,10 @@
         <v>206</v>
       </c>
       <c r="E49">
-        <v>3278</v>
+        <v>3966</v>
       </c>
       <c r="F49">
-        <v>4665</v>
+        <v>6488</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -1801,10 +1801,10 @@
         <v>413</v>
       </c>
       <c r="E50">
-        <v>1366</v>
+        <v>2501</v>
       </c>
       <c r="F50">
-        <v>4665</v>
+        <v>6488</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -1830,10 +1830,10 @@
         <v>685</v>
       </c>
       <c r="E51">
-        <v>1366</v>
+        <v>2501</v>
       </c>
       <c r="F51">
-        <v>4665</v>
+        <v>6488</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -1856,13 +1856,13 @@
         </is>
       </c>
       <c r="D52">
-        <v>268</v>
+        <v>1403</v>
       </c>
       <c r="E52">
-        <v>1366</v>
+        <v>2501</v>
       </c>
       <c r="F52">
-        <v>4665</v>
+        <v>6488</v>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -1891,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="F53">
-        <v>4665</v>
+        <v>6488</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
         <v>0</v>
       </c>
       <c r="F54">
-        <v>3485</v>
+        <v>5975</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -1949,7 +1949,7 @@
         <v>2</v>
       </c>
       <c r="F55">
-        <v>3485</v>
+        <v>5975</v>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="D56">
-        <v>2223</v>
+        <v>3497</v>
       </c>
       <c r="E56">
-        <v>2450</v>
+        <v>3724</v>
       </c>
       <c r="F56">
-        <v>3485</v>
+        <v>5975</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2004,10 +2004,10 @@
         <v>190</v>
       </c>
       <c r="E57">
-        <v>2450</v>
+        <v>3724</v>
       </c>
       <c r="F57">
-        <v>3485</v>
+        <v>5975</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
         <v>37</v>
       </c>
       <c r="E58">
-        <v>2450</v>
+        <v>3724</v>
       </c>
       <c r="F58">
-        <v>3485</v>
+        <v>5975</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2062,10 +2062,10 @@
         <v>685</v>
       </c>
       <c r="E59">
-        <v>1033</v>
+        <v>2249</v>
       </c>
       <c r="F59">
-        <v>3485</v>
+        <v>5975</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2088,13 +2088,13 @@
         </is>
       </c>
       <c r="D60">
-        <v>348</v>
+        <v>1564</v>
       </c>
       <c r="E60">
-        <v>1033</v>
+        <v>2249</v>
       </c>
       <c r="F60">
-        <v>3485</v>
+        <v>5975</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>0</v>
       </c>
       <c r="F61">
-        <v>3485</v>
+        <v>5975</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2152,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="F62">
-        <v>2418</v>
+        <v>4354</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2181,7 +2181,7 @@
         <v>0</v>
       </c>
       <c r="F63">
-        <v>2418</v>
+        <v>4354</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2204,13 +2204,13 @@
         </is>
       </c>
       <c r="D64">
-        <v>1144</v>
+        <v>1923</v>
       </c>
       <c r="E64">
-        <v>1503</v>
+        <v>2282</v>
       </c>
       <c r="F64">
-        <v>2418</v>
+        <v>4354</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -2236,10 +2236,10 @@
         <v>339</v>
       </c>
       <c r="E65">
-        <v>1503</v>
+        <v>2282</v>
       </c>
       <c r="F65">
-        <v>2418</v>
+        <v>4354</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -2265,10 +2265,10 @@
         <v>20</v>
       </c>
       <c r="E66">
-        <v>1503</v>
+        <v>2282</v>
       </c>
       <c r="F66">
-        <v>2418</v>
+        <v>4354</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -2294,10 +2294,10 @@
         <v>685</v>
       </c>
       <c r="E67">
-        <v>915</v>
+        <v>2072</v>
       </c>
       <c r="F67">
-        <v>2418</v>
+        <v>4354</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="D68">
-        <v>230</v>
+        <v>1387</v>
       </c>
       <c r="E68">
-        <v>915</v>
+        <v>2072</v>
       </c>
       <c r="F68">
-        <v>2418</v>
+        <v>4354</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -2355,7 +2355,7 @@
         <v>0</v>
       </c>
       <c r="F69">
-        <v>2418</v>
+        <v>4354</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>0</v>
       </c>
       <c r="F70">
-        <v>1374</v>
+        <v>2700</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>0</v>
       </c>
       <c r="F71">
-        <v>1374</v>
+        <v>2700</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -2436,13 +2436,13 @@
         </is>
       </c>
       <c r="D72">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="E72">
-        <v>416</v>
+        <v>606</v>
       </c>
       <c r="F72">
-        <v>1374</v>
+        <v>2700</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -2468,10 +2468,10 @@
         <v>384</v>
       </c>
       <c r="E73">
-        <v>416</v>
+        <v>606</v>
       </c>
       <c r="F73">
-        <v>1374</v>
+        <v>2700</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -2497,10 +2497,10 @@
         <v>21</v>
       </c>
       <c r="E74">
-        <v>416</v>
+        <v>606</v>
       </c>
       <c r="F74">
-        <v>1374</v>
+        <v>2700</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -2526,10 +2526,10 @@
         <v>685</v>
       </c>
       <c r="E75">
-        <v>958</v>
+        <v>2094</v>
       </c>
       <c r="F75">
-        <v>1374</v>
+        <v>2700</v>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -2552,13 +2552,13 @@
         </is>
       </c>
       <c r="D76">
-        <v>273</v>
+        <v>1409</v>
       </c>
       <c r="E76">
-        <v>958</v>
+        <v>2094</v>
       </c>
       <c r="F76">
-        <v>1374</v>
+        <v>2700</v>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
       <c r="F77">
-        <v>1374</v>
+        <v>2700</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -2616,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="F78">
-        <v>1058</v>
+        <v>2102</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -2645,7 +2645,7 @@
         <v>0</v>
       </c>
       <c r="F79">
-        <v>1058</v>
+        <v>2102</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -2668,13 +2668,13 @@
         </is>
       </c>
       <c r="D80">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="E80">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="F80">
-        <v>1058</v>
+        <v>2102</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -2700,10 +2700,10 @@
         <v>75</v>
       </c>
       <c r="E81">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="F81">
-        <v>1058</v>
+        <v>2102</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -2729,10 +2729,10 @@
         <v>14</v>
       </c>
       <c r="E82">
-        <v>105</v>
+        <v>195</v>
       </c>
       <c r="F82">
-        <v>1058</v>
+        <v>2102</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -2758,10 +2758,10 @@
         <v>689</v>
       </c>
       <c r="E83">
-        <v>953</v>
+        <v>1907</v>
       </c>
       <c r="F83">
-        <v>1058</v>
+        <v>2102</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -2784,13 +2784,13 @@
         </is>
       </c>
       <c r="D84">
-        <v>264</v>
+        <v>1218</v>
       </c>
       <c r="E84">
-        <v>953</v>
+        <v>1907</v>
       </c>
       <c r="F84">
-        <v>1058</v>
+        <v>2102</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>0</v>
       </c>
       <c r="F85">
-        <v>1058</v>
+        <v>2102</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>0</v>
       </c>
       <c r="F86">
-        <v>1026</v>
+        <v>2154</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -2877,7 +2877,7 @@
         <v>0</v>
       </c>
       <c r="F87">
-        <v>1026</v>
+        <v>2154</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -2900,13 +2900,13 @@
         </is>
       </c>
       <c r="D88">
-        <v>12</v>
+        <v>229</v>
       </c>
       <c r="E88">
-        <v>30</v>
+        <v>247</v>
       </c>
       <c r="F88">
-        <v>1026</v>
+        <v>2154</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -2932,10 +2932,10 @@
         <v>0</v>
       </c>
       <c r="E89">
-        <v>30</v>
+        <v>247</v>
       </c>
       <c r="F89">
-        <v>1026</v>
+        <v>2154</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -2961,10 +2961,10 @@
         <v>18</v>
       </c>
       <c r="E90">
-        <v>30</v>
+        <v>247</v>
       </c>
       <c r="F90">
-        <v>1026</v>
+        <v>2154</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -2990,10 +2990,10 @@
         <v>693</v>
       </c>
       <c r="E91">
-        <v>996</v>
+        <v>1907</v>
       </c>
       <c r="F91">
-        <v>1026</v>
+        <v>2154</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -3016,13 +3016,13 @@
         </is>
       </c>
       <c r="D92">
-        <v>303</v>
+        <v>1214</v>
       </c>
       <c r="E92">
-        <v>996</v>
+        <v>1907</v>
       </c>
       <c r="F92">
-        <v>1026</v>
+        <v>2154</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -3051,7 +3051,7 @@
         <v>0</v>
       </c>
       <c r="F93">
-        <v>1026</v>
+        <v>2154</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -3080,7 +3080,7 @@
         <v>0</v>
       </c>
       <c r="F94">
-        <v>1001</v>
+        <v>2023</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -3109,7 +3109,7 @@
         <v>0</v>
       </c>
       <c r="F95">
-        <v>1001</v>
+        <v>2023</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -3132,13 +3132,13 @@
         </is>
       </c>
       <c r="D96">
-        <v>30</v>
+        <v>119</v>
       </c>
       <c r="E96">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="F96">
-        <v>1001</v>
+        <v>2023</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -3164,10 +3164,10 @@
         <v>0</v>
       </c>
       <c r="E97">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="F97">
-        <v>1001</v>
+        <v>2023</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -3193,10 +3193,10 @@
         <v>22</v>
       </c>
       <c r="E98">
-        <v>52</v>
+        <v>141</v>
       </c>
       <c r="F98">
-        <v>1001</v>
+        <v>2023</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -3222,10 +3222,10 @@
         <v>698</v>
       </c>
       <c r="E99">
-        <v>949</v>
+        <v>1882</v>
       </c>
       <c r="F99">
-        <v>1001</v>
+        <v>2023</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -3248,13 +3248,13 @@
         </is>
       </c>
       <c r="D100">
-        <v>251</v>
+        <v>1184</v>
       </c>
       <c r="E100">
-        <v>949</v>
+        <v>1882</v>
       </c>
       <c r="F100">
-        <v>1001</v>
+        <v>2023</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="F101">
-        <v>1001</v>
+        <v>2023</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="F102">
-        <v>889</v>
+        <v>1872</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="F103">
-        <v>889</v>
+        <v>1872</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
@@ -3364,13 +3364,13 @@
         </is>
       </c>
       <c r="D104">
-        <v>14</v>
+        <v>126</v>
       </c>
       <c r="E104">
-        <v>31</v>
+        <v>143</v>
       </c>
       <c r="F104">
-        <v>889</v>
+        <v>1872</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
@@ -3396,10 +3396,10 @@
         <v>0</v>
       </c>
       <c r="E105">
-        <v>31</v>
+        <v>143</v>
       </c>
       <c r="F105">
-        <v>889</v>
+        <v>1872</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
@@ -3425,10 +3425,10 @@
         <v>17</v>
       </c>
       <c r="E106">
-        <v>31</v>
+        <v>143</v>
       </c>
       <c r="F106">
-        <v>889</v>
+        <v>1872</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -3454,10 +3454,10 @@
         <v>702</v>
       </c>
       <c r="E107">
-        <v>858</v>
+        <v>1729</v>
       </c>
       <c r="F107">
-        <v>889</v>
+        <v>1872</v>
       </c>
       <c r="G107" t="inlineStr">
         <is>
@@ -3480,13 +3480,13 @@
         </is>
       </c>
       <c r="D108">
-        <v>156</v>
+        <v>1027</v>
       </c>
       <c r="E108">
-        <v>858</v>
+        <v>1729</v>
       </c>
       <c r="F108">
-        <v>889</v>
+        <v>1872</v>
       </c>
       <c r="G108" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>0</v>
       </c>
       <c r="F109">
-        <v>889</v>
+        <v>1872</v>
       </c>
       <c r="G109" t="inlineStr">
         <is>
@@ -3544,7 +3544,7 @@
         <v>0</v>
       </c>
       <c r="F110">
-        <v>894</v>
+        <v>1705</v>
       </c>
       <c r="G110" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="F111">
-        <v>894</v>
+        <v>1705</v>
       </c>
       <c r="G111" t="inlineStr">
         <is>
@@ -3596,13 +3596,13 @@
         </is>
       </c>
       <c r="D112">
-        <v>11</v>
+        <v>141</v>
       </c>
       <c r="E112">
-        <v>32</v>
+        <v>162</v>
       </c>
       <c r="F112">
-        <v>894</v>
+        <v>1705</v>
       </c>
       <c r="G112" t="inlineStr">
         <is>
@@ -3628,10 +3628,10 @@
         <v>0</v>
       </c>
       <c r="E113">
-        <v>32</v>
+        <v>162</v>
       </c>
       <c r="F113">
-        <v>894</v>
+        <v>1705</v>
       </c>
       <c r="G113" t="inlineStr">
         <is>
@@ -3657,10 +3657,10 @@
         <v>21</v>
       </c>
       <c r="E114">
-        <v>32</v>
+        <v>162</v>
       </c>
       <c r="F114">
-        <v>894</v>
+        <v>1705</v>
       </c>
       <c r="G114" t="inlineStr">
         <is>
@@ -3686,10 +3686,10 @@
         <v>706</v>
       </c>
       <c r="E115">
-        <v>862</v>
+        <v>1543</v>
       </c>
       <c r="F115">
-        <v>894</v>
+        <v>1705</v>
       </c>
       <c r="G115" t="inlineStr">
         <is>
@@ -3712,13 +3712,13 @@
         </is>
       </c>
       <c r="D116">
-        <v>156</v>
+        <v>837</v>
       </c>
       <c r="E116">
-        <v>862</v>
+        <v>1543</v>
       </c>
       <c r="F116">
-        <v>894</v>
+        <v>1705</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>0</v>
       </c>
       <c r="F117">
-        <v>894</v>
+        <v>1705</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>0</v>
       </c>
       <c r="F118">
-        <v>896</v>
+        <v>1625</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
@@ -3805,7 +3805,7 @@
         <v>0</v>
       </c>
       <c r="F119">
-        <v>896</v>
+        <v>1625</v>
       </c>
       <c r="G119" t="inlineStr">
         <is>
@@ -3828,13 +3828,13 @@
         </is>
       </c>
       <c r="D120">
-        <v>11</v>
+        <v>116</v>
       </c>
       <c r="E120">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="F120">
-        <v>896</v>
+        <v>1625</v>
       </c>
       <c r="G120" t="inlineStr">
         <is>
@@ -3860,10 +3860,10 @@
         <v>0</v>
       </c>
       <c r="E121">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="F121">
-        <v>896</v>
+        <v>1625</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
@@ -3889,10 +3889,10 @@
         <v>18</v>
       </c>
       <c r="E122">
-        <v>29</v>
+        <v>134</v>
       </c>
       <c r="F122">
-        <v>896</v>
+        <v>1625</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -3918,10 +3918,10 @@
         <v>711</v>
       </c>
       <c r="E123">
-        <v>867</v>
+        <v>1491</v>
       </c>
       <c r="F123">
-        <v>896</v>
+        <v>1625</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -3944,13 +3944,13 @@
         </is>
       </c>
       <c r="D124">
-        <v>156</v>
+        <v>780</v>
       </c>
       <c r="E124">
-        <v>867</v>
+        <v>1491</v>
       </c>
       <c r="F124">
-        <v>896</v>
+        <v>1625</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -3979,7 +3979,7 @@
         <v>0</v>
       </c>
       <c r="F125">
-        <v>896</v>
+        <v>1625</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -4008,7 +4008,7 @@
         <v>0</v>
       </c>
       <c r="F126">
-        <v>903</v>
+        <v>1748</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -4037,7 +4037,7 @@
         <v>0</v>
       </c>
       <c r="F127">
-        <v>903</v>
+        <v>1748</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -4060,13 +4060,13 @@
         </is>
       </c>
       <c r="D128">
-        <v>13</v>
+        <v>127</v>
       </c>
       <c r="E128">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="F128">
-        <v>903</v>
+        <v>1748</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -4092,10 +4092,10 @@
         <v>0</v>
       </c>
       <c r="E129">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="F129">
-        <v>903</v>
+        <v>1748</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
@@ -4121,10 +4121,10 @@
         <v>18</v>
       </c>
       <c r="E130">
-        <v>31</v>
+        <v>145</v>
       </c>
       <c r="F130">
-        <v>903</v>
+        <v>1748</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
@@ -4150,10 +4150,10 @@
         <v>716</v>
       </c>
       <c r="E131">
-        <v>872</v>
+        <v>1603</v>
       </c>
       <c r="F131">
-        <v>903</v>
+        <v>1748</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
@@ -4176,13 +4176,13 @@
         </is>
       </c>
       <c r="D132">
-        <v>156</v>
+        <v>887</v>
       </c>
       <c r="E132">
-        <v>872</v>
+        <v>1603</v>
       </c>
       <c r="F132">
-        <v>903</v>
+        <v>1748</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
@@ -4211,7 +4211,7 @@
         <v>0</v>
       </c>
       <c r="F133">
-        <v>903</v>
+        <v>1748</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4240,7 +4240,7 @@
         <v>0</v>
       </c>
       <c r="F134">
-        <v>901</v>
+        <v>1913</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
@@ -4269,7 +4269,7 @@
         <v>0</v>
       </c>
       <c r="F135">
-        <v>901</v>
+        <v>1913</v>
       </c>
       <c r="G135" t="inlineStr">
         <is>
@@ -4292,13 +4292,13 @@
         </is>
       </c>
       <c r="D136">
-        <v>11</v>
+        <v>126</v>
       </c>
       <c r="E136">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="F136">
-        <v>901</v>
+        <v>1913</v>
       </c>
       <c r="G136" t="inlineStr">
         <is>
@@ -4324,10 +4324,10 @@
         <v>0</v>
       </c>
       <c r="E137">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="F137">
-        <v>901</v>
+        <v>1913</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -4353,10 +4353,10 @@
         <v>14</v>
       </c>
       <c r="E138">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="F138">
-        <v>901</v>
+        <v>1913</v>
       </c>
       <c r="G138" t="inlineStr">
         <is>
@@ -4382,10 +4382,10 @@
         <v>720</v>
       </c>
       <c r="E139">
-        <v>876</v>
+        <v>1773</v>
       </c>
       <c r="F139">
-        <v>901</v>
+        <v>1913</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="D140">
-        <v>156</v>
+        <v>1053</v>
       </c>
       <c r="E140">
-        <v>876</v>
+        <v>1773</v>
       </c>
       <c r="F140">
-        <v>901</v>
+        <v>1913</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>0</v>
       </c>
       <c r="F141">
-        <v>901</v>
+        <v>1913</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
@@ -4472,7 +4472,7 @@
         <v>0</v>
       </c>
       <c r="F142">
-        <v>908</v>
+        <v>1845</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
         <v>0</v>
       </c>
       <c r="F143">
-        <v>908</v>
+        <v>1845</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
@@ -4524,13 +4524,13 @@
         </is>
       </c>
       <c r="D144">
-        <v>11</v>
+        <v>172</v>
       </c>
       <c r="E144">
-        <v>27</v>
+        <v>188</v>
       </c>
       <c r="F144">
-        <v>908</v>
+        <v>1845</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
@@ -4556,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="E145">
-        <v>27</v>
+        <v>188</v>
       </c>
       <c r="F145">
-        <v>908</v>
+        <v>1845</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
@@ -4585,10 +4585,10 @@
         <v>16</v>
       </c>
       <c r="E146">
-        <v>27</v>
+        <v>188</v>
       </c>
       <c r="F146">
-        <v>908</v>
+        <v>1845</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
@@ -4614,10 +4614,10 @@
         <v>725</v>
       </c>
       <c r="E147">
-        <v>881</v>
+        <v>1657</v>
       </c>
       <c r="F147">
-        <v>908</v>
+        <v>1845</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
@@ -4640,13 +4640,13 @@
         </is>
       </c>
       <c r="D148">
-        <v>156</v>
+        <v>932</v>
       </c>
       <c r="E148">
-        <v>881</v>
+        <v>1657</v>
       </c>
       <c r="F148">
-        <v>908</v>
+        <v>1845</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
@@ -4675,7 +4675,7 @@
         <v>0</v>
       </c>
       <c r="F149">
-        <v>908</v>
+        <v>1845</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
@@ -4704,7 +4704,7 @@
         <v>0</v>
       </c>
       <c r="F150">
-        <v>760</v>
+        <v>1090</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
@@ -4733,7 +4733,7 @@
         <v>0</v>
       </c>
       <c r="F151">
-        <v>760</v>
+        <v>1090</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
@@ -4756,13 +4756,13 @@
         </is>
       </c>
       <c r="D152">
-        <v>11</v>
+        <v>208</v>
       </c>
       <c r="E152">
-        <v>30</v>
+        <v>227</v>
       </c>
       <c r="F152">
-        <v>760</v>
+        <v>1090</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
@@ -4788,10 +4788,10 @@
         <v>0</v>
       </c>
       <c r="E153">
-        <v>30</v>
+        <v>227</v>
       </c>
       <c r="F153">
-        <v>760</v>
+        <v>1090</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
@@ -4817,10 +4817,10 @@
         <v>19</v>
       </c>
       <c r="E154">
-        <v>30</v>
+        <v>227</v>
       </c>
       <c r="F154">
-        <v>760</v>
+        <v>1090</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
@@ -4846,10 +4846,10 @@
         <v>730</v>
       </c>
       <c r="E155">
-        <v>730</v>
+        <v>863</v>
       </c>
       <c r="F155">
-        <v>760</v>
+        <v>1090</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
@@ -4872,13 +4872,13 @@
         </is>
       </c>
       <c r="D156">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E156">
-        <v>730</v>
+        <v>863</v>
       </c>
       <c r="F156">
-        <v>760</v>
+        <v>1090</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="F157">
-        <v>760</v>
+        <v>1090</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
@@ -4936,7 +4936,7 @@
         <v>0</v>
       </c>
       <c r="F158">
-        <v>808</v>
+        <v>977</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
@@ -4965,7 +4965,7 @@
         <v>0</v>
       </c>
       <c r="F159">
-        <v>808</v>
+        <v>977</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
@@ -4988,13 +4988,13 @@
         </is>
       </c>
       <c r="D160">
-        <v>11</v>
+        <v>180</v>
       </c>
       <c r="E160">
-        <v>73</v>
+        <v>242</v>
       </c>
       <c r="F160">
-        <v>808</v>
+        <v>977</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
@@ -5020,10 +5020,10 @@
         <v>0</v>
       </c>
       <c r="E161">
-        <v>73</v>
+        <v>242</v>
       </c>
       <c r="F161">
-        <v>808</v>
+        <v>977</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
@@ -5049,10 +5049,10 @@
         <v>62</v>
       </c>
       <c r="E162">
-        <v>73</v>
+        <v>242</v>
       </c>
       <c r="F162">
-        <v>808</v>
+        <v>977</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>735</v>
       </c>
       <c r="F163">
-        <v>808</v>
+        <v>977</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>735</v>
       </c>
       <c r="F164">
-        <v>808</v>
+        <v>977</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
@@ -5139,7 +5139,7 @@
         <v>0</v>
       </c>
       <c r="F165">
-        <v>808</v>
+        <v>977</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
@@ -5168,7 +5168,7 @@
         <v>0</v>
       </c>
       <c r="F166">
-        <v>834</v>
+        <v>1180</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
@@ -5197,7 +5197,7 @@
         <v>0</v>
       </c>
       <c r="F167">
-        <v>834</v>
+        <v>1180</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
@@ -5220,13 +5220,13 @@
         </is>
       </c>
       <c r="D168">
-        <v>67</v>
+        <v>280</v>
       </c>
       <c r="E168">
-        <v>94</v>
+        <v>307</v>
       </c>
       <c r="F168">
-        <v>834</v>
+        <v>1180</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
@@ -5252,10 +5252,10 @@
         <v>0</v>
       </c>
       <c r="E169">
-        <v>94</v>
+        <v>307</v>
       </c>
       <c r="F169">
-        <v>834</v>
+        <v>1180</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
@@ -5281,10 +5281,10 @@
         <v>27</v>
       </c>
       <c r="E170">
-        <v>94</v>
+        <v>307</v>
       </c>
       <c r="F170">
-        <v>834</v>
+        <v>1180</v>
       </c>
       <c r="G170" t="inlineStr">
         <is>
@@ -5310,10 +5310,10 @@
         <v>740</v>
       </c>
       <c r="E171">
-        <v>740</v>
+        <v>873</v>
       </c>
       <c r="F171">
-        <v>834</v>
+        <v>1180</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="D172">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E172">
-        <v>740</v>
+        <v>873</v>
       </c>
       <c r="F172">
-        <v>834</v>
+        <v>1180</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
@@ -5371,7 +5371,7 @@
         <v>0</v>
       </c>
       <c r="F173">
-        <v>834</v>
+        <v>1180</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
@@ -5400,7 +5400,7 @@
         <v>0</v>
       </c>
       <c r="F174">
-        <v>773</v>
+        <v>1041</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
@@ -5429,7 +5429,7 @@
         <v>0</v>
       </c>
       <c r="F175">
-        <v>773</v>
+        <v>1041</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
@@ -5452,13 +5452,13 @@
         </is>
       </c>
       <c r="D176">
-        <v>1</v>
+        <v>136</v>
       </c>
       <c r="E176">
-        <v>28</v>
+        <v>163</v>
       </c>
       <c r="F176">
-        <v>773</v>
+        <v>1041</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
@@ -5484,10 +5484,10 @@
         <v>0</v>
       </c>
       <c r="E177">
-        <v>28</v>
+        <v>163</v>
       </c>
       <c r="F177">
-        <v>773</v>
+        <v>1041</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
@@ -5513,10 +5513,10 @@
         <v>27</v>
       </c>
       <c r="E178">
-        <v>28</v>
+        <v>163</v>
       </c>
       <c r="F178">
-        <v>773</v>
+        <v>1041</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
@@ -5542,10 +5542,10 @@
         <v>745</v>
       </c>
       <c r="E179">
-        <v>745</v>
+        <v>878</v>
       </c>
       <c r="F179">
-        <v>773</v>
+        <v>1041</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
@@ -5568,13 +5568,13 @@
         </is>
       </c>
       <c r="D180">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E180">
-        <v>745</v>
+        <v>878</v>
       </c>
       <c r="F180">
-        <v>773</v>
+        <v>1041</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
@@ -5603,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="F181">
-        <v>773</v>
+        <v>1041</v>
       </c>
       <c r="G181" t="inlineStr">
         <is>
@@ -5632,7 +5632,7 @@
         <v>0</v>
       </c>
       <c r="F182">
-        <v>779</v>
+        <v>958</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>0</v>
       </c>
       <c r="F183">
-        <v>779</v>
+        <v>958</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
@@ -5684,13 +5684,13 @@
         </is>
       </c>
       <c r="D184">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="E184">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="F184">
-        <v>779</v>
+        <v>958</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -5716,10 +5716,10 @@
         <v>0</v>
       </c>
       <c r="E185">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="F185">
-        <v>779</v>
+        <v>958</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -5745,10 +5745,10 @@
         <v>27</v>
       </c>
       <c r="E186">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="F186">
-        <v>779</v>
+        <v>958</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -5774,10 +5774,10 @@
         <v>751</v>
       </c>
       <c r="E187">
-        <v>751</v>
+        <v>884</v>
       </c>
       <c r="F187">
-        <v>779</v>
+        <v>958</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
@@ -5800,13 +5800,13 @@
         </is>
       </c>
       <c r="D188">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E188">
-        <v>751</v>
+        <v>884</v>
       </c>
       <c r="F188">
-        <v>779</v>
+        <v>958</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
         <v>0</v>
       </c>
       <c r="F189">
-        <v>779</v>
+        <v>958</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>0</v>
       </c>
       <c r="F190">
-        <v>765</v>
+        <v>944</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
         <v>0</v>
       </c>
       <c r="F191">
-        <v>765</v>
+        <v>944</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -5916,13 +5916,13 @@
         </is>
       </c>
       <c r="D192">
-        <v>1</v>
+        <v>47</v>
       </c>
       <c r="E192">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="F192">
-        <v>765</v>
+        <v>944</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -5948,10 +5948,10 @@
         <v>0</v>
       </c>
       <c r="E193">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="F193">
-        <v>765</v>
+        <v>944</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -5977,10 +5977,10 @@
         <v>7</v>
       </c>
       <c r="E194">
-        <v>8</v>
+        <v>54</v>
       </c>
       <c r="F194">
-        <v>765</v>
+        <v>944</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -6006,10 +6006,10 @@
         <v>757</v>
       </c>
       <c r="E195">
-        <v>757</v>
+        <v>890</v>
       </c>
       <c r="F195">
-        <v>765</v>
+        <v>944</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -6032,13 +6032,13 @@
         </is>
       </c>
       <c r="D196">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E196">
-        <v>757</v>
+        <v>890</v>
       </c>
       <c r="F196">
-        <v>765</v>
+        <v>944</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -6067,7 +6067,7 @@
         <v>0</v>
       </c>
       <c r="F197">
-        <v>765</v>
+        <v>944</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>0</v>
       </c>
       <c r="F198">
-        <v>444</v>
+        <v>620</v>
       </c>
       <c r="G198" t="inlineStr">
         <is>
@@ -6125,7 +6125,7 @@
         <v>0</v>
       </c>
       <c r="F199">
-        <v>444</v>
+        <v>620</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
@@ -6148,13 +6148,13 @@
         </is>
       </c>
       <c r="D200">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="E200">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="F200">
-        <v>444</v>
+        <v>620</v>
       </c>
       <c r="G200" t="inlineStr">
         <is>
@@ -6180,10 +6180,10 @@
         <v>0</v>
       </c>
       <c r="E201">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="F201">
-        <v>444</v>
+        <v>620</v>
       </c>
       <c r="G201" t="inlineStr">
         <is>
@@ -6209,10 +6209,10 @@
         <v>7</v>
       </c>
       <c r="E202">
-        <v>8</v>
+        <v>51</v>
       </c>
       <c r="F202">
-        <v>444</v>
+        <v>620</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -6238,10 +6238,10 @@
         <v>436</v>
       </c>
       <c r="E203">
-        <v>436</v>
+        <v>569</v>
       </c>
       <c r="F203">
-        <v>444</v>
+        <v>620</v>
       </c>
       <c r="G203" t="inlineStr">
         <is>
@@ -6264,13 +6264,13 @@
         </is>
       </c>
       <c r="D204">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E204">
-        <v>436</v>
+        <v>569</v>
       </c>
       <c r="F204">
-        <v>444</v>
+        <v>620</v>
       </c>
       <c r="G204" t="inlineStr">
         <is>
@@ -6299,7 +6299,7 @@
         <v>0</v>
       </c>
       <c r="F205">
-        <v>444</v>
+        <v>620</v>
       </c>
       <c r="G205" t="inlineStr">
         <is>
@@ -6328,7 +6328,7 @@
         <v>0</v>
       </c>
       <c r="F206">
-        <v>8</v>
+        <v>177</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
@@ -6357,7 +6357,7 @@
         <v>0</v>
       </c>
       <c r="F207">
-        <v>8</v>
+        <v>177</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
@@ -6380,13 +6380,13 @@
         </is>
       </c>
       <c r="D208">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="E208">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F208">
-        <v>8</v>
+        <v>177</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
@@ -6412,10 +6412,10 @@
         <v>0</v>
       </c>
       <c r="E209">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F209">
-        <v>8</v>
+        <v>177</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
@@ -6441,10 +6441,10 @@
         <v>7</v>
       </c>
       <c r="E210">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="F210">
-        <v>8</v>
+        <v>177</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
@@ -6470,10 +6470,10 @@
         <v>0</v>
       </c>
       <c r="E211">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F211">
-        <v>8</v>
+        <v>177</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
@@ -6496,13 +6496,13 @@
         </is>
       </c>
       <c r="D212">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E212">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F212">
-        <v>8</v>
+        <v>177</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>0</v>
       </c>
       <c r="F213">
-        <v>8</v>
+        <v>177</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
@@ -6560,7 +6560,7 @@
         <v>0</v>
       </c>
       <c r="F214">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>0</v>
       </c>
       <c r="F215">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="G215" t="inlineStr">
         <is>
@@ -6612,13 +6612,13 @@
         </is>
       </c>
       <c r="D216">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E216">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F216">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
@@ -6644,10 +6644,10 @@
         <v>0</v>
       </c>
       <c r="E217">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F217">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="G217" t="inlineStr">
         <is>
@@ -6673,10 +6673,10 @@
         <v>7</v>
       </c>
       <c r="E218">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F218">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="G218" t="inlineStr">
         <is>
@@ -6702,10 +6702,10 @@
         <v>0</v>
       </c>
       <c r="E219">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F219">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="G219" t="inlineStr">
         <is>
@@ -6728,13 +6728,13 @@
         </is>
       </c>
       <c r="D220">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E220">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F220">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="G220" t="inlineStr">
         <is>
@@ -6763,7 +6763,7 @@
         <v>0</v>
       </c>
       <c r="F221">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="G221" t="inlineStr">
         <is>
@@ -6792,7 +6792,7 @@
         <v>0</v>
       </c>
       <c r="F222">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="G222" t="inlineStr">
         <is>
@@ -6821,7 +6821,7 @@
         <v>0</v>
       </c>
       <c r="F223">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="G223" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>8</v>
       </c>
       <c r="F224">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="G224" t="inlineStr">
         <is>
@@ -6879,7 +6879,7 @@
         <v>8</v>
       </c>
       <c r="F225">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="G225" t="inlineStr">
         <is>
@@ -6908,7 +6908,7 @@
         <v>8</v>
       </c>
       <c r="F226">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
@@ -6934,10 +6934,10 @@
         <v>0</v>
       </c>
       <c r="E227">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F227">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="G227" t="inlineStr">
         <is>
@@ -6960,13 +6960,13 @@
         </is>
       </c>
       <c r="D228">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E228">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F228">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="G228" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>0</v>
       </c>
       <c r="F229">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="G229" t="inlineStr">
         <is>
@@ -7024,7 +7024,7 @@
         <v>0</v>
       </c>
       <c r="F230">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="G230" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>0</v>
       </c>
       <c r="F231">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>8</v>
       </c>
       <c r="F232">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="G232" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>8</v>
       </c>
       <c r="F233">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="G233" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>8</v>
       </c>
       <c r="F234">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>
@@ -7166,10 +7166,10 @@
         <v>0</v>
       </c>
       <c r="E235">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F235">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="G235" t="inlineStr">
         <is>
@@ -7192,13 +7192,13 @@
         </is>
       </c>
       <c r="D236">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E236">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F236">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="G236" t="inlineStr">
         <is>
@@ -7227,7 +7227,7 @@
         <v>0</v>
       </c>
       <c r="F237">
-        <v>8</v>
+        <v>141</v>
       </c>
       <c r="G237" t="inlineStr">
         <is>
@@ -7256,7 +7256,7 @@
         <v>0</v>
       </c>
       <c r="F238">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="G238" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>0</v>
       </c>
       <c r="F239">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="G239" t="inlineStr">
         <is>
@@ -7308,13 +7308,13 @@
         </is>
       </c>
       <c r="D240">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="E240">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="F240">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="G240" t="inlineStr">
         <is>
@@ -7340,10 +7340,10 @@
         <v>0</v>
       </c>
       <c r="E241">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="F241">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="G241" t="inlineStr">
         <is>
@@ -7369,10 +7369,10 @@
         <v>7</v>
       </c>
       <c r="E242">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="F242">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -7398,10 +7398,10 @@
         <v>0</v>
       </c>
       <c r="E243">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F243">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="G243" t="inlineStr">
         <is>
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="D244">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E244">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F244">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="G244" t="inlineStr">
         <is>
@@ -7459,7 +7459,7 @@
         <v>0</v>
       </c>
       <c r="F245">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="G245" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>0</v>
       </c>
       <c r="F246">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="G246" t="inlineStr">
         <is>
@@ -7517,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="F247">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="G247" t="inlineStr">
         <is>
@@ -7540,13 +7540,13 @@
         </is>
       </c>
       <c r="D248">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="E248">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="F248">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
@@ -7572,10 +7572,10 @@
         <v>0</v>
       </c>
       <c r="E249">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="F249">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="G249" t="inlineStr">
         <is>
@@ -7601,10 +7601,10 @@
         <v>7</v>
       </c>
       <c r="E250">
-        <v>8</v>
+        <v>59</v>
       </c>
       <c r="F250">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="G250" t="inlineStr">
         <is>
@@ -7630,10 +7630,10 @@
         <v>0</v>
       </c>
       <c r="E251">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F251">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="G251" t="inlineStr">
         <is>
@@ -7656,13 +7656,13 @@
         </is>
       </c>
       <c r="D252">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E252">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F252">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="G252" t="inlineStr">
         <is>
@@ -7691,7 +7691,7 @@
         <v>0</v>
       </c>
       <c r="F253">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="G253" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>0</v>
       </c>
       <c r="F254">
-        <v>7</v>
+        <v>191</v>
       </c>
       <c r="G254" t="inlineStr">
         <is>
@@ -7749,7 +7749,7 @@
         <v>0</v>
       </c>
       <c r="F255">
-        <v>7</v>
+        <v>191</v>
       </c>
       <c r="G255" t="inlineStr">
         <is>
@@ -7772,13 +7772,13 @@
         </is>
       </c>
       <c r="D256">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="E256">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="F256">
-        <v>7</v>
+        <v>191</v>
       </c>
       <c r="G256" t="inlineStr">
         <is>
@@ -7804,10 +7804,10 @@
         <v>0</v>
       </c>
       <c r="E257">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="F257">
-        <v>7</v>
+        <v>191</v>
       </c>
       <c r="G257" t="inlineStr">
         <is>
@@ -7833,10 +7833,10 @@
         <v>7</v>
       </c>
       <c r="E258">
-        <v>7</v>
+        <v>58</v>
       </c>
       <c r="F258">
-        <v>7</v>
+        <v>191</v>
       </c>
       <c r="G258" t="inlineStr">
         <is>
@@ -7862,10 +7862,10 @@
         <v>0</v>
       </c>
       <c r="E259">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F259">
-        <v>7</v>
+        <v>191</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
@@ -7888,13 +7888,13 @@
         </is>
       </c>
       <c r="D260">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E260">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F260">
-        <v>7</v>
+        <v>191</v>
       </c>
       <c r="G260" t="inlineStr">
         <is>
@@ -7923,7 +7923,7 @@
         <v>0</v>
       </c>
       <c r="F261">
-        <v>7</v>
+        <v>191</v>
       </c>
       <c r="G261" t="inlineStr">
         <is>
@@ -7952,7 +7952,7 @@
         <v>0</v>
       </c>
       <c r="F262">
-        <v>44</v>
+        <v>228</v>
       </c>
       <c r="G262" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>0</v>
       </c>
       <c r="F263">
-        <v>44</v>
+        <v>228</v>
       </c>
       <c r="G263" t="inlineStr">
         <is>
@@ -8004,13 +8004,13 @@
         </is>
       </c>
       <c r="D264">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="E264">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="F264">
-        <v>44</v>
+        <v>228</v>
       </c>
       <c r="G264" t="inlineStr">
         <is>
@@ -8036,10 +8036,10 @@
         <v>0</v>
       </c>
       <c r="E265">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="F265">
-        <v>44</v>
+        <v>228</v>
       </c>
       <c r="G265" t="inlineStr">
         <is>
@@ -8065,10 +8065,10 @@
         <v>44</v>
       </c>
       <c r="E266">
-        <v>44</v>
+        <v>95</v>
       </c>
       <c r="F266">
-        <v>44</v>
+        <v>228</v>
       </c>
       <c r="G266" t="inlineStr">
         <is>
@@ -8094,10 +8094,10 @@
         <v>0</v>
       </c>
       <c r="E267">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F267">
-        <v>44</v>
+        <v>228</v>
       </c>
       <c r="G267" t="inlineStr">
         <is>
@@ -8120,13 +8120,13 @@
         </is>
       </c>
       <c r="D268">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="E268">
-        <v>0</v>
+        <v>133</v>
       </c>
       <c r="F268">
-        <v>44</v>
+        <v>228</v>
       </c>
       <c r="G268" t="inlineStr">
         <is>
@@ -8155,7 +8155,7 @@
         <v>0</v>
       </c>
       <c r="F269">
-        <v>44</v>
+        <v>228</v>
       </c>
       <c r="G269" t="inlineStr">
         <is>
